--- a/measurement-course/files/w11/data.xlsx
+++ b/measurement-course/files/w11/data.xlsx
@@ -38454,7 +38454,7 @@
   </sheetData>
   <conditionalFormatting sqref="P21:P50">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(P21,4)="تمييز"</formula>
+      <formula>LEFT(P21,5)="تمييز"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>P21="جيدة"</formula>
